--- a/doc/Project-info.xlsx
+++ b/doc/Project-info.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="90">
   <si>
     <t xml:space="preserve">#</t>
   </si>
@@ -30,6 +30,9 @@
     <t xml:space="preserve">Location</t>
   </si>
   <si>
+    <t xml:space="preserve">::source</t>
+  </si>
+  <si>
     <t xml:space="preserve">`::search-in`</t>
   </si>
   <si>
@@ -54,10 +57,13 @@
     <t xml:space="preserve">Current basis</t>
   </si>
   <si>
+    <t xml:space="preserve">`['current-basis]`</t>
+  </si>
+  <si>
     <t xml:space="preserve">`:basis`</t>
   </si>
   <si>
-    <t xml:space="preserve">`:current-basis`</t>
+    <t xml:space="preserve">`:deps-edn`</t>
   </si>
   <si>
     <t xml:space="preserve">RUN, DEV</t>
@@ -78,13 +84,13 @@
     <t xml:space="preserve">Initial basis</t>
   </si>
   <si>
-    <t xml:space="preserve">`:initial-basis`</t>
+    <t xml:space="preserve">`['initial-basis]`</t>
   </si>
   <si>
     <t xml:space="preserve">Current `:basis-config` `:project` map</t>
   </si>
   <si>
-    <t xml:space="preserve">`:edn`</t>
+    <t xml:space="preserve">`['current-basis :basis-config :project]`</t>
   </si>
   <si>
     <t xml:space="preserve">CLI?</t>
@@ -93,6 +99,9 @@
     <t xml:space="preserve">`clojure.tools.deps.edn/project-deps`</t>
   </si>
   <si>
+    <t xml:space="preserve">`['project-deps]`</t>
+  </si>
+  <si>
     <t xml:space="preserve">`:project`</t>
   </si>
   <si>
@@ -102,57 +111,75 @@
     <t xml:space="preserve">WD</t>
   </si>
   <si>
-    <t xml:space="preserve">Custom `deps.edn` path from current basis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`:file`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BC, CLI?</t>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`deps.edn`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`["deps.edn"]`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`:deps-edn-file`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`:deps-edn-rsrc`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JAR, UJAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U, RO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JAR, DSRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`/deps.edn`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`["/deps.edn"]`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U, RO, RT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`deps/&lt;group-id&gt;/&lt;artifact-id&gt;/deps.edn` </t>
+  </si>
+  <si>
+    <t xml:space="preserve">`["deps/&lt;group-id&gt;/&lt;artifact-id&gt;/deps.edn"]`</t>
   </si>
   <si>
     <t xml:space="preserve">`:resource`</t>
   </si>
   <si>
-    <t xml:space="preserve">RUN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BC, CLI?, U, RO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`deps.edn`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JAR, UJAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U, RO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JAR, DSRC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`/deps.edn`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U, RO, RT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`deps/&lt;group-id&gt;/&lt;artifact-id&gt;/deps.edn` </t>
-  </si>
-  <si>
     <t xml:space="preserve">RO</t>
   </si>
   <si>
+    <t xml:space="preserve">8</t>
+  </si>
+  <si>
     <t xml:space="preserve">`/deps/&lt;group-id&gt;/&lt;artifact-id&gt;/deps.edn` </t>
   </si>
   <si>
+    <t xml:space="preserve">`["/deps/&lt;group-id&gt;/&lt;artifact-id&gt;/deps.edn"]`</t>
+  </si>
+  <si>
     <t xml:space="preserve">RO, RT</t>
   </si>
   <si>
@@ -255,16 +282,7 @@
     <t xml:space="preserve">Runtime Only</t>
   </si>
   <si>
-    <t xml:space="preserve">Intended for runtime use only. May also be picked up at dev/ops time, but other locations should be preferred and searched first.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Basis Config</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A file path is created with the `:dir` and/or `:project` entries from `:basis-config` (doc), and searched as a file then as a resource, unless it points to the default project `deps.edn`.</t>
+    <t xml:space="preserve">Intended for runtime use only. A resource `deps.edn` may be picked up at dev/ops time, but other locations should be preferred and searched first.</t>
   </si>
   <si>
     <t xml:space="preserve">RT</t>
@@ -284,7 +302,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -308,16 +326,21 @@
       <family val="0"/>
     </font>
     <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF000000"/>
+      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
@@ -365,56 +388,48 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -427,11 +442,27 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -557,395 +588,382 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I1048576"/>
+  <dimension ref="A1:J1048576"/>
   <sheetFormatPr defaultColWidth="9.34375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="36.32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="5.8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="4.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="9.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="12.6"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="1" width="9.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="33.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="36.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="12.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="5.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="4.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="9.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="12.6"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="13" style="2" width="9.34"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="true" ht="17.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+    <row r="1" customFormat="false" ht="17.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>9</v>
+      <c r="B2" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="17.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="4" customFormat="false" ht="17.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>10</v>
+      <c r="B4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="17.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>15</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="17.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>22</v>
+      <c r="B5" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="17.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
+      <c r="G6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="17.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" s="5" customFormat="true" ht="17.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I7" s="5" t="s">
+      <c r="E7" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="17.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C8" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="17.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="D8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>24</v>
+        <v>38</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="C9" s="1" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C10" s="1" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="F10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="17.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="I10" s="1" t="s">
+      <c r="J11" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="17.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="17.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="17.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F12" s="1" t="s">
+      <c r="G12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="G12" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="17.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="17.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="J12" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
@@ -954,7 +972,6 @@
     <hyperlink ref="B3" r:id="rId2" location="clojure.java.basis/initial-basis" display="Initial basis"/>
     <hyperlink ref="B4" r:id="rId3" display="Current `:basis-config` `:project` map"/>
     <hyperlink ref="B5" r:id="rId4" location="clojure.tools.deps.edn/project-deps" display="`clojure.tools.deps.edn/project-deps`"/>
-    <hyperlink ref="B6" r:id="rId5" location="basis_config" display="Custom `deps.edn` path from current basis"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>
@@ -974,130 +991,131 @@
   <dimension ref="A1:H1048576"/>
   <sheetFormatPr defaultColWidth="9.34375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="4.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="7" width="12.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="6" width="4.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="7" width="21.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="6" width="4.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="7" width="23.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="6" width="4.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="7" width="36.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="4.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="12.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="8" width="4.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="21.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="8" width="4.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="23.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="8" width="4.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="36.61"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="2" width="9.34"/>
   </cols>
   <sheetData>
-    <row r="1" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="8"/>
-      <c r="B1" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="8" t="s">
+    <row r="1" s="10" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9"/>
+      <c r="B1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="E1" s="8" t="s">
+      <c r="C1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="G1" s="8" t="s">
+      <c r="D1" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="9" t="s">
-        <v>46</v>
+      <c r="F1" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>51</v>
+      <c r="A2" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>55</v>
+      <c r="A3" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>60</v>
+      <c r="A4" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G5" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>62</v>
+      <c r="G5" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G6" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>64</v>
+      <c r="G6" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G7" s="7"/>
+      <c r="G7" s="2"/>
     </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
@@ -1116,108 +1134,97 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C1048576"/>
   <sheetFormatPr defaultColWidth="9.34375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="10" width="5.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="11" width="12.06"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="5" width="60.9"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="4" style="12" width="9.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="11" width="5.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="12" width="12.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="7" width="60.9"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="4" style="13" width="9.34"/>
   </cols>
   <sheetData>
-    <row r="1" s="16" customFormat="true" ht="17.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="C1" s="15" t="s">
-        <v>8</v>
+    <row r="1" s="17" customFormat="true" ht="17.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>68</v>
+      <c r="A2" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="32.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>70</v>
+      <c r="A3" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>72</v>
+      <c r="A4" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="32.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>75</v>
+      <c r="A5" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="32.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="17.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="32.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
+      <c r="A6" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="32.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" location="cache_dir" display="The runtime basis is set as a JVM system property by the clojure CLI host-specific scripts, and is cached on disk (doc)."/>
     <hyperlink ref="C4" r:id="rId2" location="with-dir" display="The function `clojure.tools.deps.util.dir/with-dir` (doc) may be used to specify a custom project directory."/>
-    <hyperlink ref="C7" r:id="rId3" location="basis_config" display="A file path is created with the `:dir` and/or `:project` entries from `:basis-config` (doc), and searched as a file then as a resource, unless it points to the default project `deps.edn`."/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>
